--- a/Landers_DB24_shared.xlsx
+++ b/Landers_DB24_shared.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D11592-1A82-49FB-BA6C-6E04EFF489A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F7089-DE1D-4641-9F24-92458F287660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00204FEE-323F-4DA1-86F4-8FD253E43B4D}"/>
+    <workbookView xWindow="-28920" yWindow="1680" windowWidth="29040" windowHeight="15720" xr2:uid="{00204FEE-323F-4DA1-86F4-8FD253E43B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="All Landers" sheetId="1" r:id="rId1"/>
@@ -1296,7 +1296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="190">
   <si>
     <t>year</t>
   </si>
@@ -1965,6 +1965,9 @@
     <t>https://nssdc.gsfc.nasa.gov/nmc/spacecraft/display.action?id=IM-1-NOVA
 Isp from SpaceX raptor value for that fuel</t>
   </si>
+  <si>
+    <t>NSSDC, https://history.nasa.gov/wp-content/uploads/static/history/alsj/SurveyorProgramResultsNASA-SP-184.pdf</t>
+  </si>
 </sst>
 </file>
 
@@ -2243,30 +2246,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2306,6 +2285,30 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4959,7 +4962,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9C85EE5A-F540-4E0F-AAB0-AAB592D63F8B}" type="CELLRANGE">
+                    <a:fld id="{26F5AC42-E7B1-479C-932F-D65BEC900351}" type="CELLRANGE">
                       <a:rPr lang="fr-FR"/>
                       <a:pPr/>
                       <a:t>[PLAGECELL]</a:t>
@@ -7043,7 +7046,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9AB46360-A548-4D4B-B4BB-9B12895D8AC3}" type="CELLRANGE">
+                    <a:fld id="{DA36F10A-6C52-4D62-A0D5-1C46EC8839AB}" type="CELLRANGE">
                       <a:rPr lang="fr-FR"/>
                       <a:pPr/>
                       <a:t>[PLAGECELL]</a:t>
@@ -7196,7 +7199,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A4D47F56-FBD6-4F78-BC5F-7B861B7500B2}" type="CELLRANGE">
+                    <a:fld id="{620FDBB3-C0CA-405A-A6D0-EBCD99DE65B5}" type="CELLRANGE">
                       <a:rPr lang="fr-FR"/>
                       <a:pPr/>
                       <a:t>[PLAGECELL]</a:t>
@@ -7229,7 +7232,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{333A8D5B-59B7-4364-844E-C58D5DF3F2E4}" type="CELLRANGE">
+                    <a:fld id="{CDDD998E-D48F-440B-B849-17F5D868B7A5}" type="CELLRANGE">
                       <a:rPr lang="fr-FR"/>
                       <a:pPr/>
                       <a:t>[PLAGECELL]</a:t>
@@ -11326,19 +11329,19 @@
                   <c:v>708</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>667.90000000000009</c:v>
+                  <c:v>700.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>697</c:v>
+                  <c:v>727</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>670</c:v>
+                  <c:v>702</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>697</c:v>
+                  <c:v>726</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>700</c:v>
+                  <c:v>733</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3130</c:v>
@@ -17239,19 +17242,19 @@
                   <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>294.3</c:v>
+                  <c:v>262</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>296</c:v>
+                  <c:v>266</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>303</c:v>
+                  <c:v>271</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>296</c:v>
+                  <c:v>267</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>306</c:v>
+                  <c:v>273</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1814</c:v>
@@ -17820,19 +17823,19 @@
                   <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>294.3</c:v>
+                  <c:v>262</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>296</c:v>
+                  <c:v>266</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>303</c:v>
+                  <c:v>271</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>296</c:v>
+                  <c:v>267</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>306</c:v>
+                  <c:v>273</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1814</c:v>
@@ -17958,19 +17961,19 @@
                   <c:v>708</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>667.90000000000009</c:v>
+                  <c:v>700.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>697</c:v>
+                  <c:v>727</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>670</c:v>
+                  <c:v>702</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>697</c:v>
+                  <c:v>726</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>700</c:v>
+                  <c:v>733</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3130</c:v>
@@ -37386,110 +37389,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34">
+      <c r="A3" s="26">
         <v>1966</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="26">
         <v>1538</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="26">
         <v>847</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="28">
         <v>99.8</v>
       </c>
-      <c r="G3" s="34">
-        <f>D3-E3-F3</f>
+      <c r="G3" s="26">
+        <f t="shared" ref="G3:G9" si="0">D3-E3-F3</f>
         <v>591.20000000000005</v>
       </c>
-      <c r="H3" s="34">
-        <f>D3-G3</f>
+      <c r="H3" s="26">
+        <f t="shared" ref="H3:H4" si="1">D3-G3</f>
         <v>946.8</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="36">
+      <c r="J3" s="28">
         <v>287</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="26">
         <v>2630</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="M3" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="N3" s="29" t="s">
         <v>93</v>
       </c>
       <c r="O3" t="s">
@@ -37497,48 +37500,48 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38">
+      <c r="A4" s="30">
         <v>1966</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="30">
         <v>1620</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="30">
         <v>800</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="30">
         <v>112</v>
       </c>
-      <c r="G4" s="38">
-        <f>D4-E4-F4</f>
+      <c r="G4" s="30">
+        <f t="shared" si="0"/>
         <v>708</v>
       </c>
-      <c r="H4" s="38">
-        <f>D4-G4</f>
+      <c r="H4" s="30">
+        <f t="shared" si="1"/>
         <v>912</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="30">
         <v>287</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="30">
         <v>1880</v>
       </c>
-      <c r="L4" s="38" t="s">
+      <c r="L4" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="39" t="s">
+      <c r="M4" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="N4" s="40" t="s">
+      <c r="N4" s="32" t="s">
         <v>95</v>
       </c>
       <c r="O4" t="s">
@@ -37546,278 +37549,273 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41">
+      <c r="A5" s="33">
         <v>1966</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="33">
         <v>995.2</v>
       </c>
-      <c r="E5" s="41">
-        <v>294.3</v>
-      </c>
-      <c r="F5" s="41">
+      <c r="E5" s="33">
+        <v>262</v>
+      </c>
+      <c r="F5" s="33">
         <v>33</v>
       </c>
-      <c r="G5" s="41">
-        <f>D5-E5-F5</f>
-        <v>667.90000000000009</v>
-      </c>
-      <c r="H5" s="41">
-        <f>D5-G5</f>
-        <v>327.29999999999995</v>
-      </c>
-      <c r="I5" s="41" t="s">
+      <c r="G5" s="33">
+        <f t="shared" si="0"/>
+        <v>700.2</v>
+      </c>
+      <c r="H5" s="33">
+        <v>295</v>
+      </c>
+      <c r="I5" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="33">
         <v>230</v>
       </c>
-      <c r="K5" s="50"/>
-      <c r="L5" s="41" t="s">
+      <c r="K5" s="42"/>
+      <c r="L5" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M5" s="48" t="s">
+      <c r="M5" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="N5" s="43" t="s">
-        <v>84</v>
+      <c r="N5" s="35" t="s">
+        <v>189</v>
       </c>
       <c r="O5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38">
+      <c r="A6" s="30">
         <v>1967</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="30">
         <v>1026</v>
       </c>
-      <c r="E6" s="38">
-        <v>296</v>
-      </c>
-      <c r="F6" s="38">
+      <c r="E6" s="30">
+        <v>266</v>
+      </c>
+      <c r="F6" s="30">
         <v>33</v>
       </c>
-      <c r="G6" s="38">
-        <f>D6-E6-F6</f>
-        <v>697</v>
-      </c>
-      <c r="H6" s="38">
-        <f>D6-G6</f>
-        <v>329</v>
-      </c>
-      <c r="I6" s="38" t="s">
+      <c r="G6" s="30">
+        <f t="shared" si="0"/>
+        <v>727</v>
+      </c>
+      <c r="H6" s="30">
+        <v>299</v>
+      </c>
+      <c r="I6" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="30">
         <v>230</v>
       </c>
-      <c r="K6" s="50"/>
-      <c r="L6" s="38" t="s">
+      <c r="K6" s="42"/>
+      <c r="L6" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M6" s="49" t="s">
+      <c r="M6" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="N6" s="40" t="s">
-        <v>84</v>
+      <c r="N6" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="O6" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41">
+      <c r="A7" s="33">
         <v>1967</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="33">
         <v>1006</v>
       </c>
-      <c r="E7" s="41">
-        <v>303</v>
-      </c>
-      <c r="F7" s="41">
+      <c r="E7" s="33">
+        <v>271</v>
+      </c>
+      <c r="F7" s="33">
         <v>33</v>
       </c>
-      <c r="G7" s="41">
-        <f>D7-E7-F7</f>
-        <v>670</v>
-      </c>
-      <c r="H7" s="41">
-        <f>D7-G7</f>
-        <v>336</v>
-      </c>
-      <c r="I7" s="41" t="s">
+      <c r="G7" s="33">
+        <f t="shared" si="0"/>
+        <v>702</v>
+      </c>
+      <c r="H7" s="33">
+        <v>304</v>
+      </c>
+      <c r="I7" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="33">
         <v>230</v>
       </c>
-      <c r="K7" s="50"/>
-      <c r="L7" s="41" t="s">
+      <c r="K7" s="42"/>
+      <c r="L7" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M7" s="48" t="s">
+      <c r="M7" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="N7" s="43" t="s">
-        <v>84</v>
+      <c r="N7" s="35" t="s">
+        <v>189</v>
       </c>
       <c r="O7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38">
+      <c r="A8" s="30">
         <v>1967</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="38">
+      <c r="C8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="30">
         <v>1026</v>
       </c>
-      <c r="E8" s="38">
-        <v>296</v>
-      </c>
-      <c r="F8" s="38">
+      <c r="E8" s="30">
+        <v>267</v>
+      </c>
+      <c r="F8" s="30">
         <v>33</v>
       </c>
-      <c r="G8" s="38">
-        <f>D8-E8-F8</f>
-        <v>697</v>
-      </c>
-      <c r="H8" s="38">
-        <f>D8-G8</f>
-        <v>329</v>
-      </c>
-      <c r="I8" s="38" t="s">
+      <c r="G8" s="30">
+        <f t="shared" si="0"/>
+        <v>726</v>
+      </c>
+      <c r="H8" s="30">
+        <v>300</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="30">
         <v>230</v>
       </c>
-      <c r="K8" s="50"/>
-      <c r="L8" s="38" t="s">
+      <c r="K8" s="42"/>
+      <c r="L8" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="49" t="s">
+      <c r="M8" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="N8" s="40" t="s">
-        <v>84</v>
+      <c r="N8" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="O8" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41">
+      <c r="A9" s="33">
         <v>1968</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="33">
         <v>1039</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="33">
+        <v>273</v>
+      </c>
+      <c r="F9" s="33">
+        <v>33</v>
+      </c>
+      <c r="G9" s="33">
+        <f t="shared" si="0"/>
+        <v>733</v>
+      </c>
+      <c r="H9" s="33">
         <v>306</v>
       </c>
-      <c r="F9" s="41">
-        <v>33</v>
-      </c>
-      <c r="G9" s="41">
-        <f>D9-E9-F9</f>
-        <v>700</v>
-      </c>
-      <c r="H9" s="41">
-        <f>D9-G9</f>
-        <v>339</v>
-      </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="33">
         <v>230</v>
       </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="41" t="s">
+      <c r="K9" s="42"/>
+      <c r="L9" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M9" s="48" t="s">
+      <c r="M9" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="N9" s="42" t="s">
-        <v>84</v>
+      <c r="N9" s="35" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38">
+      <c r="A10" s="30">
         <v>1968</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="30">
         <v>5700</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="30">
         <v>1814</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="30">
         <v>756</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="30">
         <v>3130</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="30">
         <v>2570</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="30">
         <v>314</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="30">
         <v>1880</v>
       </c>
-      <c r="L10" s="39" t="s">
+      <c r="L10" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="M10" s="39" t="s">
+      <c r="M10" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="N10" s="39" t="s">
+      <c r="N10" s="31" t="s">
         <v>95</v>
       </c>
       <c r="O10" t="s">
@@ -37825,46 +37823,46 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="41">
+      <c r="A11" s="33">
         <v>1969</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="33">
         <v>5750</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="33">
         <v>1880</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="33">
         <v>520</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="33">
         <v>3350</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="33">
         <v>2400</v>
       </c>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="33">
         <v>314</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="33">
         <v>1880</v>
       </c>
-      <c r="L11" s="42" t="s">
+      <c r="L11" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="42" t="s">
+      <c r="M11" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="42" t="s">
+      <c r="N11" s="34" t="s">
         <v>105</v>
       </c>
       <c r="O11" t="s">
@@ -37872,48 +37870,48 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38">
+      <c r="A12" s="30">
         <v>1969</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="30">
         <v>15065</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="30">
         <v>2034</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="30">
         <v>4819</v>
       </c>
-      <c r="G12" s="38">
-        <f>D12-E12-F12</f>
+      <c r="G12" s="30">
+        <f t="shared" ref="G12:G43" si="2">D12-E12-F12</f>
         <v>8212</v>
       </c>
-      <c r="H12" s="38">
-        <f>D12-G12</f>
+      <c r="H12" s="30">
+        <f t="shared" ref="H12:H48" si="3">D12-G12</f>
         <v>6853</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12" s="30">
         <v>311</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="30">
         <v>2273</v>
       </c>
-      <c r="L12" s="38" t="s">
+      <c r="L12" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M12" s="39" t="s">
+      <c r="M12" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="N12" s="40" t="s">
+      <c r="N12" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O12" t="s">
@@ -37921,48 +37919,48 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="41">
+      <c r="A13" s="33">
         <v>1969</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="33">
         <v>15103</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="33">
         <v>2034</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="33">
         <v>4821</v>
       </c>
-      <c r="G13" s="41">
-        <f>D13-E13-F13</f>
+      <c r="G13" s="33">
+        <f t="shared" si="2"/>
         <v>8248</v>
       </c>
-      <c r="H13" s="41">
-        <f>D13-G13</f>
+      <c r="H13" s="33">
+        <f t="shared" si="3"/>
         <v>6855</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="33">
         <v>311</v>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="33">
         <v>2261</v>
       </c>
-      <c r="L13" s="41" t="s">
+      <c r="L13" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="N13" s="43" t="s">
+      <c r="N13" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O13" t="s">
@@ -37970,48 +37968,48 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38">
+      <c r="A14" s="30">
         <v>1970</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="30">
         <v>14916</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="30">
         <v>2109</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="30">
         <v>4489</v>
       </c>
-      <c r="G14" s="38">
-        <f>D14-E14-F14</f>
+      <c r="G14" s="30">
+        <f t="shared" si="2"/>
         <v>8318</v>
       </c>
-      <c r="H14" s="38">
-        <f>D14-G14</f>
+      <c r="H14" s="30">
+        <f t="shared" si="3"/>
         <v>6598</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="I14" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14" s="30">
         <v>311</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="30">
         <v>2263</v>
       </c>
-      <c r="L14" s="38" t="s">
+      <c r="L14" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M14" s="39" t="s">
+      <c r="M14" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="N14" s="40" t="s">
+      <c r="N14" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O14" t="s">
@@ -38019,48 +38017,48 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41">
+      <c r="A15" s="33">
         <v>1971</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="33">
         <v>15034</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="33">
         <v>2134</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="33">
         <v>4700</v>
       </c>
-      <c r="G15" s="41">
-        <f>D15-E15-F15</f>
+      <c r="G15" s="33">
+        <f t="shared" si="2"/>
         <v>8200</v>
       </c>
-      <c r="H15" s="41">
-        <f>D15-G15</f>
+      <c r="H15" s="33">
+        <f t="shared" si="3"/>
         <v>6834</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="33">
         <v>311</v>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="33">
         <v>2263</v>
       </c>
-      <c r="L15" s="41" t="s">
+      <c r="L15" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M15" s="42" t="s">
+      <c r="M15" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="N15" s="43" t="s">
+      <c r="N15" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O15" t="s">
@@ -38068,48 +38066,48 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="38">
+      <c r="A16" s="30">
         <v>1971</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="30">
         <v>16447</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="30">
         <v>2626</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="30">
         <v>4795</v>
       </c>
-      <c r="G16" s="38">
-        <f>D16-E16-F16</f>
+      <c r="G16" s="30">
+        <f t="shared" si="2"/>
         <v>9026</v>
       </c>
-      <c r="H16" s="38">
-        <f>D16-G16</f>
+      <c r="H16" s="30">
+        <f t="shared" si="3"/>
         <v>7421</v>
       </c>
-      <c r="I16" s="38" t="s">
+      <c r="I16" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16" s="30">
         <v>311</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16" s="30">
         <v>2250</v>
       </c>
-      <c r="L16" s="38" t="s">
+      <c r="L16" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M16" s="39" t="s">
+      <c r="M16" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="N16" s="40" t="s">
+      <c r="N16" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O16" t="s">
@@ -38117,48 +38115,48 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="41">
+      <c r="A17" s="33">
         <v>1972</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="33">
         <v>16447</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="33">
         <v>2626</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="33">
         <v>4795</v>
       </c>
-      <c r="G17" s="41">
-        <f>D17-E17-F17</f>
+      <c r="G17" s="33">
+        <f t="shared" si="2"/>
         <v>9026</v>
       </c>
-      <c r="H17" s="41">
-        <f>D17-G17</f>
+      <c r="H17" s="33">
+        <f t="shared" si="3"/>
         <v>7421</v>
       </c>
-      <c r="I17" s="41" t="s">
+      <c r="I17" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="33">
         <v>311</v>
       </c>
-      <c r="K17" s="41">
+      <c r="K17" s="33">
         <v>2267</v>
       </c>
-      <c r="L17" s="41" t="s">
+      <c r="L17" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M17" s="42" t="s">
+      <c r="M17" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="N17" s="43" t="s">
+      <c r="N17" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O17" t="s">
@@ -38166,48 +38164,48 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="38">
+      <c r="A18" s="30">
         <v>1972</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="30">
         <v>16447</v>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="30">
         <v>2626</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="30">
         <v>4795</v>
       </c>
-      <c r="G18" s="38">
-        <f>D18-E18-F18</f>
+      <c r="G18" s="30">
+        <f t="shared" si="2"/>
         <v>9026</v>
       </c>
-      <c r="H18" s="38">
-        <f>D18-G18</f>
+      <c r="H18" s="30">
+        <f t="shared" si="3"/>
         <v>7421</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="J18" s="38">
+      <c r="J18" s="30">
         <v>311</v>
       </c>
-      <c r="K18" s="38">
+      <c r="K18" s="30">
         <v>2265</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M18" s="39" t="s">
+      <c r="M18" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="N18" s="40" t="s">
+      <c r="N18" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O18" t="s">
@@ -38215,48 +38213,48 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="41">
+      <c r="A19" s="33">
         <v>1988</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="33">
         <v>54463</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="33">
         <v>9823</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="33">
         <v>14000</v>
       </c>
-      <c r="G19" s="41">
-        <f>D19-E19-F19</f>
+      <c r="G19" s="33">
+        <f t="shared" si="2"/>
         <v>30640</v>
       </c>
-      <c r="H19" s="41">
-        <f>D19-G19</f>
+      <c r="H19" s="33">
+        <f t="shared" si="3"/>
         <v>23823</v>
       </c>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="33">
         <v>451</v>
       </c>
-      <c r="K19" s="41">
+      <c r="K19" s="33">
         <v>4380</v>
       </c>
-      <c r="L19" s="41" t="s">
+      <c r="L19" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M19" s="42" t="s">
+      <c r="M19" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="N19" s="43" t="s">
+      <c r="N19" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O19" t="s">
@@ -38264,48 +38262,48 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38">
+      <c r="A20" s="30">
         <v>1988</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="30">
         <v>67326</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="30">
         <v>7899</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="30">
         <v>14000</v>
       </c>
-      <c r="G20" s="38">
-        <f>D20-E20-F20</f>
+      <c r="G20" s="30">
+        <f t="shared" si="2"/>
         <v>45427</v>
       </c>
-      <c r="H20" s="38">
-        <f>D20-G20</f>
+      <c r="H20" s="30">
+        <f t="shared" si="3"/>
         <v>21899</v>
       </c>
-      <c r="I20" s="38" t="s">
+      <c r="I20" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="J20" s="38">
+      <c r="J20" s="30">
         <v>333</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20" s="30">
         <v>4380</v>
       </c>
-      <c r="L20" s="38" t="s">
+      <c r="L20" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M20" s="39" t="s">
+      <c r="M20" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="N20" s="40" t="s">
+      <c r="N20" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O20" t="s">
@@ -38313,93 +38311,93 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41">
+      <c r="A21" s="33">
         <v>1988</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="33">
         <v>48218</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="33">
         <v>9823</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="33">
         <v>6000</v>
       </c>
-      <c r="G21" s="41">
-        <f>D21-E21-F21</f>
+      <c r="G21" s="33">
+        <f t="shared" si="2"/>
         <v>32395</v>
       </c>
-      <c r="H21" s="41">
-        <f>D21-G21</f>
+      <c r="H21" s="33">
+        <f t="shared" si="3"/>
         <v>15823</v>
       </c>
-      <c r="I21" s="41" t="s">
+      <c r="I21" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="33">
         <v>451</v>
       </c>
-      <c r="K21" s="41">
+      <c r="K21" s="33">
         <v>4380</v>
       </c>
-      <c r="L21" s="41" t="s">
+      <c r="L21" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M21" s="42" t="s">
+      <c r="M21" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="N21" s="43"/>
+      <c r="N21" s="35"/>
       <c r="O21" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38">
+      <c r="A22" s="30">
         <v>1988</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="30">
         <v>60075</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="30">
         <v>9823</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="30">
         <v>25000</v>
       </c>
-      <c r="G22" s="38">
-        <f>D22-E22-F22</f>
+      <c r="G22" s="30">
+        <f t="shared" si="2"/>
         <v>25252</v>
       </c>
-      <c r="H22" s="38">
-        <f>D22-G22</f>
+      <c r="H22" s="30">
+        <f t="shared" si="3"/>
         <v>34823</v>
       </c>
-      <c r="I22" s="38" t="s">
+      <c r="I22" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="30">
         <v>451</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22" s="30">
         <v>2100</v>
       </c>
-      <c r="L22" s="38" t="s">
+      <c r="L22" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40" t="s">
+      <c r="M22" s="31"/>
+      <c r="N22" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O22" t="s">
@@ -38407,46 +38405,46 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="41">
+      <c r="A23" s="33">
         <v>1988</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="33">
         <v>69298</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="33">
         <v>7899</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="33">
         <v>25000</v>
       </c>
-      <c r="G23" s="41">
-        <f>D23-E23-F23</f>
+      <c r="G23" s="33">
+        <f t="shared" si="2"/>
         <v>36399</v>
       </c>
-      <c r="H23" s="41">
-        <f>D23-G23</f>
+      <c r="H23" s="33">
+        <f t="shared" si="3"/>
         <v>32899</v>
       </c>
-      <c r="I23" s="41" t="s">
+      <c r="I23" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="J23" s="41">
+      <c r="J23" s="33">
         <v>333</v>
       </c>
-      <c r="K23" s="41">
+      <c r="K23" s="33">
         <v>2100</v>
       </c>
-      <c r="L23" s="41" t="s">
+      <c r="L23" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M23" s="42"/>
-      <c r="N23" s="43" t="s">
+      <c r="M23" s="34"/>
+      <c r="N23" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O23" t="s">
@@ -38454,91 +38452,91 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38">
+      <c r="A24" s="30">
         <v>1992</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="30">
         <v>93037</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="30">
         <v>12992</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="30">
         <v>35894</v>
       </c>
-      <c r="G24" s="38">
-        <f>D24-E24-F24</f>
+      <c r="G24" s="30">
+        <f t="shared" si="2"/>
         <v>44151</v>
       </c>
-      <c r="H24" s="38">
-        <f>D24-G24</f>
+      <c r="H24" s="30">
+        <f t="shared" si="3"/>
         <v>48886</v>
       </c>
-      <c r="I24" s="38" t="s">
+      <c r="I24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24" s="30">
         <v>466</v>
       </c>
-      <c r="K24" s="50"/>
-      <c r="L24" s="38" t="s">
+      <c r="K24" s="42"/>
+      <c r="L24" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M24" s="39" t="s">
+      <c r="M24" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="N24" s="40"/>
+      <c r="N24" s="32"/>
       <c r="O24" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41">
+      <c r="A25" s="33">
         <v>1992</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="33">
         <v>93038</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="33">
         <v>12472</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="33">
         <v>36384</v>
       </c>
-      <c r="G25" s="41">
-        <f>D25-E25-F25</f>
+      <c r="G25" s="33">
+        <f t="shared" si="2"/>
         <v>44182</v>
       </c>
-      <c r="H25" s="41">
-        <f>D25-G25</f>
+      <c r="H25" s="33">
+        <f t="shared" si="3"/>
         <v>48856</v>
       </c>
-      <c r="I25" s="41" t="s">
+      <c r="I25" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="41">
+      <c r="J25" s="33">
         <v>465.5</v>
       </c>
-      <c r="K25" s="50"/>
-      <c r="L25" s="41" t="s">
+      <c r="K25" s="42"/>
+      <c r="L25" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M25" s="42" t="s">
+      <c r="M25" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="N25" s="43" t="s">
+      <c r="N25" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O25" t="s">
@@ -38546,44 +38544,44 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="38">
+      <c r="A26" s="30">
         <v>1994</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="30">
         <v>3775</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="30">
         <v>530</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="30">
         <v>200</v>
       </c>
-      <c r="G26" s="38">
-        <f>D26-E26-F26</f>
+      <c r="G26" s="30">
+        <f t="shared" si="2"/>
         <v>3045</v>
       </c>
-      <c r="H26" s="38">
-        <f>D26-G26</f>
+      <c r="H26" s="30">
+        <f t="shared" si="3"/>
         <v>730</v>
       </c>
-      <c r="I26" s="38" t="s">
+      <c r="I26" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="J26" s="38">
+      <c r="J26" s="30">
         <v>320</v>
       </c>
-      <c r="K26" s="50"/>
-      <c r="L26" s="38" t="s">
+      <c r="K26" s="42"/>
+      <c r="L26" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40" t="s">
+      <c r="M26" s="31"/>
+      <c r="N26" s="32" t="s">
         <v>180</v>
       </c>
       <c r="O26" t="s">
@@ -38591,48 +38589,48 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="41">
+      <c r="A27" s="33">
         <v>1995</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="33">
         <v>5038.6000000000004</v>
       </c>
-      <c r="E27" s="41">
+      <c r="E27" s="33">
         <v>1673.7</v>
       </c>
-      <c r="F27" s="41">
+      <c r="F27" s="33">
         <v>473.3</v>
       </c>
-      <c r="G27" s="41">
-        <f>D27-E27-F27</f>
+      <c r="G27" s="33">
+        <f t="shared" si="2"/>
         <v>2891.6000000000004</v>
       </c>
-      <c r="H27" s="41">
-        <f>D27-G27</f>
+      <c r="H27" s="33">
+        <f t="shared" si="3"/>
         <v>2147</v>
       </c>
-      <c r="I27" s="41" t="s">
+      <c r="I27" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="J27" s="41">
+      <c r="J27" s="33">
         <v>300</v>
       </c>
-      <c r="K27" s="41">
+      <c r="K27" s="33">
         <v>3732</v>
       </c>
-      <c r="L27" s="41" t="s">
+      <c r="L27" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M27" s="42" t="s">
+      <c r="M27" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="N27" s="43" t="s">
+      <c r="N27" s="35" t="s">
         <v>107</v>
       </c>
       <c r="O27" t="s">
@@ -38640,48 +38638,48 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38">
+      <c r="A28" s="30">
         <v>2005</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="30">
         <v>37494</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="30">
         <v>10814</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="30">
         <v>980</v>
       </c>
-      <c r="G28" s="38">
-        <f>D28-E28-F28</f>
+      <c r="G28" s="30">
+        <f t="shared" si="2"/>
         <v>25700</v>
       </c>
-      <c r="H28" s="38">
-        <f>D28-G28</f>
+      <c r="H28" s="30">
+        <f t="shared" si="3"/>
         <v>11794</v>
       </c>
-      <c r="I28" s="38" t="s">
+      <c r="I28" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="30">
         <v>362</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="30">
         <v>3772</v>
       </c>
-      <c r="L28" s="38" t="s">
+      <c r="L28" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M28" s="39" t="s">
+      <c r="M28" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="N28" s="40" t="s">
+      <c r="N28" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O28" t="s">
@@ -38689,48 +38687,48 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="41">
+      <c r="A29" s="33">
         <v>2005</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="33">
         <v>45862</v>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="33">
         <v>7665</v>
       </c>
-      <c r="F29" s="41">
+      <c r="F29" s="33">
         <v>13102</v>
       </c>
-      <c r="G29" s="41">
-        <f>D29-E29-F29</f>
+      <c r="G29" s="33">
+        <f t="shared" si="2"/>
         <v>25095</v>
       </c>
-      <c r="H29" s="41">
-        <f>D29-G29</f>
+      <c r="H29" s="33">
+        <f t="shared" si="3"/>
         <v>20767</v>
       </c>
-      <c r="I29" s="41" t="s">
+      <c r="I29" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="J29" s="41">
+      <c r="J29" s="33">
         <v>451</v>
       </c>
-      <c r="K29" s="41">
+      <c r="K29" s="33">
         <v>1900</v>
       </c>
-      <c r="L29" s="41" t="s">
+      <c r="L29" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M29" s="42" t="s">
+      <c r="M29" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="N29" s="43" t="s">
+      <c r="N29" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O29" t="s">
@@ -38738,46 +38736,46 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="38">
+      <c r="A30" s="30">
         <v>2005</v>
       </c>
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="30">
         <v>81911</v>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="30">
         <v>9726</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="30">
         <v>42472</v>
       </c>
-      <c r="G30" s="38">
-        <f>D30-E30-F30</f>
+      <c r="G30" s="30">
+        <f t="shared" si="2"/>
         <v>29713</v>
       </c>
-      <c r="H30" s="38">
-        <f>D30-G30</f>
+      <c r="H30" s="30">
+        <f t="shared" si="3"/>
         <v>52198</v>
       </c>
-      <c r="I30" s="38" t="s">
+      <c r="I30" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30" s="30">
         <v>350</v>
       </c>
-      <c r="K30" s="38">
+      <c r="K30" s="30">
         <v>2841</v>
       </c>
-      <c r="L30" s="38" t="s">
+      <c r="L30" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40" t="s">
+      <c r="M30" s="31"/>
+      <c r="N30" s="32" t="s">
         <v>113</v>
       </c>
       <c r="O30" t="s">
@@ -38785,46 +38783,46 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="41">
+      <c r="A31" s="33">
         <v>2006</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="33">
         <v>49972</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="33">
         <v>10426</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="33">
         <v>11502</v>
       </c>
-      <c r="G31" s="41">
-        <f>D31-E31-F31</f>
+      <c r="G31" s="33">
+        <f t="shared" si="2"/>
         <v>28044</v>
       </c>
-      <c r="H31" s="41">
-        <f>D31-G31</f>
+      <c r="H31" s="33">
+        <f t="shared" si="3"/>
         <v>21928</v>
       </c>
-      <c r="I31" s="41" t="s">
+      <c r="I31" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="J31" s="41">
+      <c r="J31" s="33">
         <v>450</v>
       </c>
-      <c r="K31" s="50"/>
-      <c r="L31" s="41" t="s">
+      <c r="K31" s="42"/>
+      <c r="L31" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M31" s="42" t="s">
+      <c r="M31" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="N31" s="43" t="s">
+      <c r="N31" s="35" t="s">
         <v>113</v>
       </c>
       <c r="O31" t="s">
@@ -38832,46 +38830,46 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="38">
+      <c r="A32" s="30">
         <v>2007</v>
       </c>
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="30">
         <v>43501</v>
       </c>
-      <c r="E32" s="38">
+      <c r="E32" s="30">
         <v>8500</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32" s="30">
         <v>18634</v>
       </c>
-      <c r="G32" s="38">
-        <f>D32-E32-F32</f>
+      <c r="G32" s="30">
+        <f t="shared" si="2"/>
         <v>16367</v>
       </c>
-      <c r="H32" s="38">
-        <f>D32-G32</f>
+      <c r="H32" s="30">
+        <f t="shared" si="3"/>
         <v>27134</v>
       </c>
-      <c r="I32" s="38" t="s">
+      <c r="I32" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="J32" s="38">
+      <c r="J32" s="30">
         <v>451</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32" s="30">
         <v>2117</v>
       </c>
-      <c r="L32" s="38" t="s">
+      <c r="L32" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M32" s="39"/>
-      <c r="N32" s="40" t="s">
+      <c r="M32" s="31"/>
+      <c r="N32" s="32" t="s">
         <v>128</v>
       </c>
       <c r="O32" t="s">
@@ -38879,46 +38877,46 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="41">
+      <c r="A33" s="33">
         <v>2010</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="42" t="s">
+      <c r="C33" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="33">
         <v>462</v>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="33">
         <v>171.1</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="33">
         <v>14.9</v>
       </c>
-      <c r="G33" s="41">
-        <f>D33-E33-F33</f>
+      <c r="G33" s="33">
+        <f t="shared" si="2"/>
         <v>276</v>
       </c>
-      <c r="H33" s="41">
-        <f>D33-G33</f>
+      <c r="H33" s="33">
+        <f t="shared" si="3"/>
         <v>186</v>
       </c>
-      <c r="I33" s="41" t="s">
+      <c r="I33" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="J33" s="41">
+      <c r="J33" s="33">
         <v>160</v>
       </c>
-      <c r="K33" s="50"/>
-      <c r="L33" s="41" t="s">
+      <c r="K33" s="42"/>
+      <c r="L33" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="M33" s="42" t="s">
+      <c r="M33" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="N33" s="43" t="s">
+      <c r="N33" s="35" t="s">
         <v>90</v>
       </c>
       <c r="O33" t="s">
@@ -38926,48 +38924,48 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="38">
+      <c r="A34" s="30">
         <v>2013</v>
       </c>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D34" s="38">
+      <c r="D34" s="30">
         <v>3780</v>
       </c>
-      <c r="E34" s="38">
+      <c r="E34" s="30">
         <v>1200</v>
       </c>
-      <c r="F34" s="38">
+      <c r="F34" s="30">
         <v>170</v>
       </c>
-      <c r="G34" s="38">
-        <f>D34-E34-F34</f>
+      <c r="G34" s="30">
+        <f t="shared" si="2"/>
         <v>2410</v>
       </c>
-      <c r="H34" s="38">
-        <f>D34-G34</f>
+      <c r="H34" s="30">
+        <f t="shared" si="3"/>
         <v>1370</v>
       </c>
-      <c r="I34" s="38" t="s">
+      <c r="I34" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="J34" s="38">
+      <c r="J34" s="30">
         <v>333</v>
       </c>
-      <c r="K34" s="38">
+      <c r="K34" s="30">
         <v>1880</v>
       </c>
-      <c r="L34" s="38" t="s">
+      <c r="L34" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M34" s="39" t="s">
+      <c r="M34" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="N34" s="40" t="s">
+      <c r="N34" s="32" t="s">
         <v>99</v>
       </c>
       <c r="O34" t="s">
@@ -38975,46 +38973,46 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="41">
+      <c r="A35" s="33">
         <v>2018</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="33">
         <v>15387.2</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="33">
         <v>4687.2</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="33">
         <v>1000</v>
       </c>
-      <c r="G35" s="41">
-        <f>D35-E35-F35</f>
+      <c r="G35" s="33">
+        <f t="shared" si="2"/>
         <v>9700</v>
       </c>
-      <c r="H35" s="41">
-        <f>D35-G35</f>
+      <c r="H35" s="33">
+        <f t="shared" si="3"/>
         <v>5687.2000000000007</v>
       </c>
-      <c r="I35" s="41" t="s">
+      <c r="I35" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="J35" s="41">
+      <c r="J35" s="33">
         <v>350</v>
       </c>
-      <c r="K35" s="41">
+      <c r="K35" s="33">
         <v>3006</v>
       </c>
-      <c r="L35" s="41" t="s">
+      <c r="L35" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M35" s="42"/>
-      <c r="N35" s="43" t="s">
+      <c r="M35" s="34"/>
+      <c r="N35" s="35" t="s">
         <v>181</v>
       </c>
       <c r="O35" t="s">
@@ -39022,95 +39020,95 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="38">
+      <c r="A36" s="30">
         <v>2019</v>
       </c>
-      <c r="B36" s="38" t="s">
+      <c r="B36" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="30">
         <v>4250</v>
       </c>
-      <c r="E36" s="38">
+      <c r="E36" s="30">
         <v>1372</v>
       </c>
-      <c r="F36" s="38">
+      <c r="F36" s="30">
         <v>300</v>
       </c>
-      <c r="G36" s="38">
-        <f>D36-E36-F36</f>
+      <c r="G36" s="30">
+        <f t="shared" si="2"/>
         <v>2578</v>
       </c>
-      <c r="H36" s="38">
-        <f>D36-G36</f>
+      <c r="H36" s="30">
+        <f t="shared" si="3"/>
         <v>1672</v>
       </c>
-      <c r="I36" s="38" t="s">
+      <c r="I36" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="J36" s="38">
+      <c r="J36" s="30">
         <v>333</v>
       </c>
-      <c r="K36" s="50"/>
-      <c r="L36" s="38" t="s">
+      <c r="K36" s="42"/>
+      <c r="L36" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M36" s="39" t="s">
+      <c r="M36" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="N36" s="40" t="s">
+      <c r="N36" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="O36" s="47" t="s">
+      <c r="O36" s="39" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="41">
+      <c r="A37" s="33">
         <v>2019</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="33">
         <v>585</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="33">
         <v>150</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="33">
         <v>0</v>
       </c>
-      <c r="G37" s="41">
-        <f>D37-E37-F37</f>
+      <c r="G37" s="33">
+        <f t="shared" si="2"/>
         <v>435</v>
       </c>
-      <c r="H37" s="41">
-        <f>D37-G37</f>
+      <c r="H37" s="33">
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="I37" s="41" t="s">
+      <c r="I37" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="J37" s="41">
+      <c r="J37" s="33">
         <v>318</v>
       </c>
-      <c r="K37" s="41">
+      <c r="K37" s="33">
         <v>1930</v>
       </c>
-      <c r="L37" s="41" t="s">
+      <c r="L37" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M37" s="42" t="s">
+      <c r="M37" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="N37" s="43" t="s">
+      <c r="N37" s="35" t="s">
         <v>85</v>
       </c>
       <c r="O37" t="s">
@@ -39118,46 +39116,46 @@
       </c>
     </row>
     <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="38">
+      <c r="A38" s="30">
         <v>2019</v>
       </c>
-      <c r="B38" s="38" t="s">
+      <c r="B38" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="38">
+      <c r="D38" s="30">
         <v>1471</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="30">
         <v>626</v>
       </c>
-      <c r="F38" s="38">
+      <c r="F38" s="30">
         <v>27</v>
       </c>
-      <c r="G38" s="38">
-        <f>D38-E38-F38</f>
+      <c r="G38" s="30">
+        <f t="shared" si="2"/>
         <v>818</v>
       </c>
-      <c r="H38" s="38">
-        <f>D38-G38</f>
+      <c r="H38" s="30">
+        <f t="shared" si="3"/>
         <v>653</v>
       </c>
-      <c r="I38" s="38" t="s">
+      <c r="I38" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="J38" s="38">
+      <c r="J38" s="30">
         <v>318</v>
       </c>
-      <c r="K38" s="50"/>
-      <c r="L38" s="38" t="s">
+      <c r="K38" s="42"/>
+      <c r="L38" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M38" s="39" t="s">
+      <c r="M38" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="N38" s="40" t="s">
+      <c r="N38" s="32" t="s">
         <v>88</v>
       </c>
       <c r="O38" t="s">
@@ -39165,48 +39163,48 @@
       </c>
     </row>
     <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="41">
+      <c r="A39" s="33">
         <v>2019</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="C39" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="41">
+      <c r="D39" s="33">
         <v>3640</v>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="33">
         <v>1200</v>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="33">
         <v>170</v>
       </c>
-      <c r="G39" s="41">
-        <f>D39-E39-F39</f>
+      <c r="G39" s="33">
+        <f t="shared" si="2"/>
         <v>2270</v>
       </c>
-      <c r="H39" s="41">
-        <f>D39-G39</f>
+      <c r="H39" s="33">
+        <f t="shared" si="3"/>
         <v>1370</v>
       </c>
-      <c r="I39" s="41" t="s">
+      <c r="I39" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="33">
         <v>333</v>
       </c>
-      <c r="K39" s="41">
+      <c r="K39" s="33">
         <v>1880</v>
       </c>
-      <c r="L39" s="41" t="s">
+      <c r="L39" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="N39" s="43" t="s">
+      <c r="N39" s="35" t="s">
         <v>101</v>
       </c>
       <c r="O39" t="s">
@@ -39214,48 +39212,48 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="38">
+      <c r="A40" s="30">
         <v>2020</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D40" s="38">
+      <c r="D40" s="30">
         <v>3800</v>
       </c>
-      <c r="E40" s="38">
+      <c r="E40" s="30">
         <v>1200</v>
       </c>
-      <c r="F40" s="38">
+      <c r="F40" s="30">
         <v>800</v>
       </c>
-      <c r="G40" s="38">
-        <f>D40-E40-F40</f>
+      <c r="G40" s="30">
+        <f t="shared" si="2"/>
         <v>1800</v>
       </c>
-      <c r="H40" s="38">
-        <f>D40-G40</f>
+      <c r="H40" s="30">
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
-      <c r="I40" s="38" t="s">
+      <c r="I40" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="J40" s="38">
+      <c r="J40" s="30">
         <v>333</v>
       </c>
-      <c r="K40" s="38">
+      <c r="K40" s="30">
         <v>1930</v>
       </c>
-      <c r="L40" s="38" t="s">
+      <c r="L40" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M40" s="39" t="s">
+      <c r="M40" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="N40" s="40" t="s">
+      <c r="N40" s="32" t="s">
         <v>104</v>
       </c>
       <c r="O40" t="s">
@@ -39263,46 +39261,46 @@
       </c>
     </row>
     <row r="41" spans="1:15" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="41">
+      <c r="A41" s="33">
         <v>2022</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="41">
+      <c r="D41" s="33">
         <v>14.6</v>
       </c>
-      <c r="E41" s="41">
+      <c r="E41" s="33">
         <v>0.7</v>
       </c>
-      <c r="F41" s="41">
+      <c r="F41" s="33">
         <v>0</v>
       </c>
-      <c r="G41" s="41">
-        <f>D41-E41-F41</f>
+      <c r="G41" s="33">
+        <f t="shared" si="2"/>
         <v>13.9</v>
       </c>
-      <c r="H41" s="41">
-        <f>D41-G41</f>
+      <c r="H41" s="33">
+        <f t="shared" si="3"/>
         <v>0.69999999999999929</v>
       </c>
-      <c r="I41" s="41" t="s">
+      <c r="I41" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41">
+      <c r="J41" s="33"/>
+      <c r="K41" s="33">
         <v>2500</v>
       </c>
-      <c r="L41" s="41" t="s">
+      <c r="L41" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="M41" s="42" t="s">
+      <c r="M41" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="N41" s="43" t="s">
+      <c r="N41" s="35" t="s">
         <v>83</v>
       </c>
       <c r="O41" s="24" t="s">
@@ -39310,48 +39308,48 @@
       </c>
     </row>
     <row r="42" spans="1:15" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="38">
+      <c r="A42" s="30">
         <v>2022</v>
       </c>
-      <c r="B42" s="38" t="s">
+      <c r="B42" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="38">
+      <c r="D42" s="30">
         <v>42267</v>
       </c>
-      <c r="E42" s="38">
+      <c r="E42" s="30">
         <v>9861</v>
       </c>
-      <c r="F42" s="38">
+      <c r="F42" s="30">
         <v>9121</v>
       </c>
-      <c r="G42" s="38">
-        <f>D42-E42-F42</f>
+      <c r="G42" s="30">
+        <f t="shared" si="2"/>
         <v>23285</v>
       </c>
-      <c r="H42" s="38">
-        <f>D42-G42</f>
+      <c r="H42" s="30">
+        <f t="shared" si="3"/>
         <v>18982</v>
       </c>
-      <c r="I42" s="38" t="s">
+      <c r="I42" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="J42" s="38">
+      <c r="J42" s="30">
         <v>340</v>
       </c>
-      <c r="K42" s="38">
+      <c r="K42" s="30">
         <v>2520</v>
       </c>
-      <c r="L42" s="38" t="s">
+      <c r="L42" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="M42" s="39" t="s">
+      <c r="M42" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="N42" s="40" t="s">
+      <c r="N42" s="32" t="s">
         <v>116</v>
       </c>
       <c r="O42" s="24" t="s">
@@ -39359,46 +39357,46 @@
       </c>
     </row>
     <row r="43" spans="1:15" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="41">
+      <c r="A43" s="33">
         <v>2023</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="33">
         <v>1000</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="33">
         <v>340</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="33">
         <v>30</v>
       </c>
-      <c r="G43" s="41">
-        <f>D43-E43-F43</f>
+      <c r="G43" s="33">
+        <f t="shared" si="2"/>
         <v>630</v>
       </c>
-      <c r="H43" s="41">
-        <f>D43-G43</f>
+      <c r="H43" s="33">
+        <f t="shared" si="3"/>
         <v>370</v>
       </c>
-      <c r="I43" s="41" t="s">
+      <c r="I43" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J43" s="41">
+      <c r="J43" s="33">
         <v>333</v>
       </c>
-      <c r="K43" s="50"/>
-      <c r="L43" s="41" t="s">
+      <c r="K43" s="42"/>
+      <c r="L43" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M43" s="42" t="s">
+      <c r="M43" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="N43" s="43" t="s">
+      <c r="N43" s="35" t="s">
         <v>86</v>
       </c>
       <c r="O43" s="24" t="s">
@@ -39406,41 +39404,41 @@
       </c>
     </row>
     <row r="44" spans="1:15" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="38">
+      <c r="A44" s="30">
         <v>2023</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="30">
         <v>1750</v>
       </c>
-      <c r="E44" s="50"/>
-      <c r="F44" s="38">
+      <c r="E44" s="42"/>
+      <c r="F44" s="30">
         <v>26</v>
       </c>
-      <c r="G44" s="50"/>
-      <c r="H44" s="38">
-        <f>D44-G44</f>
+      <c r="G44" s="42"/>
+      <c r="H44" s="30">
+        <f t="shared" si="3"/>
         <v>1750</v>
       </c>
-      <c r="I44" s="38" t="s">
+      <c r="I44" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="J44" s="38">
+      <c r="J44" s="30">
         <v>318</v>
       </c>
-      <c r="K44" s="50"/>
-      <c r="L44" s="38" t="s">
+      <c r="K44" s="42"/>
+      <c r="L44" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M44" s="39" t="s">
+      <c r="M44" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="N44" s="40" t="s">
+      <c r="N44" s="32" t="s">
         <v>182</v>
       </c>
       <c r="O44" s="24" t="s">
@@ -39448,44 +39446,44 @@
       </c>
     </row>
     <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="41">
+      <c r="A45" s="33">
         <v>2023</v>
       </c>
-      <c r="B45" s="41" t="s">
+      <c r="B45" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="41">
+      <c r="D45" s="33">
         <v>1750</v>
       </c>
-      <c r="E45" s="41">
+      <c r="E45" s="33">
         <f>D45-G45-F45</f>
         <v>770</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="33">
         <v>30</v>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="33">
         <v>950</v>
       </c>
-      <c r="H45" s="41">
-        <f>D45-G45</f>
+      <c r="H45" s="33">
+        <f t="shared" si="3"/>
         <v>800</v>
       </c>
-      <c r="I45" s="41" t="s">
+      <c r="I45" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="J45" s="41">
+      <c r="J45" s="33">
         <v>333</v>
       </c>
-      <c r="K45" s="50"/>
-      <c r="L45" s="41" t="s">
+      <c r="K45" s="42"/>
+      <c r="L45" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M45" s="42"/>
-      <c r="N45" s="43" t="s">
+      <c r="M45" s="34"/>
+      <c r="N45" s="35" t="s">
         <v>176</v>
       </c>
       <c r="O45" t="s">
@@ -39493,48 +39491,48 @@
       </c>
     </row>
     <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="38">
+      <c r="A46" s="30">
         <v>2024</v>
       </c>
-      <c r="B46" s="38" t="s">
+      <c r="B46" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="30">
         <v>710</v>
       </c>
-      <c r="E46" s="38">
+      <c r="E46" s="30">
         <v>190</v>
       </c>
-      <c r="F46" s="38">
+      <c r="F46" s="30">
         <v>20</v>
       </c>
-      <c r="G46" s="38">
+      <c r="G46" s="30">
         <f>D46-E46-F46</f>
         <v>500</v>
       </c>
-      <c r="H46" s="38">
-        <f>D46-G46</f>
+      <c r="H46" s="30">
+        <f t="shared" si="3"/>
         <v>210</v>
       </c>
-      <c r="I46" s="38" t="s">
+      <c r="I46" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="J46" s="38">
+      <c r="J46" s="30">
         <v>328</v>
       </c>
-      <c r="K46" s="38">
+      <c r="K46" s="30">
         <v>2774</v>
       </c>
-      <c r="L46" s="38" t="s">
+      <c r="L46" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M46" s="39" t="s">
+      <c r="M46" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="N46" s="40" t="s">
+      <c r="N46" s="32" t="s">
         <v>169</v>
       </c>
       <c r="O46" t="s">
@@ -39542,39 +39540,39 @@
       </c>
     </row>
     <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="44">
+      <c r="A47" s="36">
         <v>2024</v>
       </c>
-      <c r="B47" s="44" t="s">
+      <c r="B47" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="D47" s="44">
+      <c r="D47" s="36">
         <v>1283</v>
       </c>
-      <c r="E47" s="50"/>
-      <c r="F47" s="44">
+      <c r="E47" s="42"/>
+      <c r="F47" s="36">
         <v>90</v>
       </c>
-      <c r="G47" s="50"/>
-      <c r="H47" s="44">
-        <f>D47-G47</f>
+      <c r="G47" s="42"/>
+      <c r="H47" s="36">
+        <f t="shared" si="3"/>
         <v>1283</v>
       </c>
-      <c r="I47" s="44" t="s">
+      <c r="I47" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="J47" s="44">
+      <c r="J47" s="36">
         <v>318</v>
       </c>
-      <c r="K47" s="50"/>
-      <c r="L47" s="44" t="s">
+      <c r="K47" s="42"/>
+      <c r="L47" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="M47" s="45"/>
-      <c r="N47" s="46" t="s">
+      <c r="M47" s="37"/>
+      <c r="N47" s="38" t="s">
         <v>177</v>
       </c>
       <c r="O47" t="s">
@@ -39582,39 +39580,39 @@
       </c>
     </row>
     <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="38">
+      <c r="A48" s="30">
         <v>2024</v>
       </c>
-      <c r="B48" s="38" t="s">
+      <c r="B48" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="C48" s="39" t="s">
+      <c r="C48" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="D48" s="38">
+      <c r="D48" s="30">
         <v>1908</v>
       </c>
-      <c r="E48" s="51"/>
-      <c r="F48" s="38">
+      <c r="E48" s="43"/>
+      <c r="F48" s="30">
         <v>100</v>
       </c>
-      <c r="G48" s="51"/>
-      <c r="H48" s="38">
-        <f>D48-G48</f>
+      <c r="G48" s="43"/>
+      <c r="H48" s="30">
+        <f t="shared" si="3"/>
         <v>1908</v>
       </c>
-      <c r="I48" s="38" t="s">
+      <c r="I48" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="J48" s="38">
+      <c r="J48" s="30">
         <v>360</v>
       </c>
-      <c r="K48" s="51"/>
-      <c r="L48" s="38" t="s">
+      <c r="K48" s="43"/>
+      <c r="L48" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M48" s="39"/>
-      <c r="N48" s="52" t="s">
+      <c r="M48" s="31"/>
+      <c r="N48" s="44" t="s">
         <v>188</v>
       </c>
       <c r="O48" t="s">
@@ -41776,11 +41774,11 @@
       <c r="P3" s="7">
         <v>1930</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="46">
         <f>AVERAGE(P3:P11)</f>
         <v>2199.1111111111113</v>
       </c>
-      <c r="R3" s="28">
+      <c r="R3" s="49">
         <f>AVERAGE(K3:K11)</f>
         <v>310.75</v>
       </c>
@@ -41802,7 +41800,7 @@
         <f>EXP(($Q$3)/($R$3*9.81))*(U3+V3)-(U3+V3)</f>
         <v>140.84030880755236</v>
       </c>
-      <c r="Y3" s="29">
+      <c r="Y3" s="50">
         <v>1.1399999999999999</v>
       </c>
       <c r="Z3" s="18">
@@ -41869,8 +41867,8 @@
       <c r="P4" s="7">
         <v>2630</v>
       </c>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="28"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="49"/>
       <c r="S4" s="7" t="s">
         <v>144</v>
       </c>
@@ -41892,7 +41890,7 @@
         <f t="shared" ref="X4:X22" si="4">EXP(($Q$3)/($R$3*9.81))*(U4+V4)-(U4+V4)</f>
         <v>281.68061761510472</v>
       </c>
-      <c r="Y4" s="29"/>
+      <c r="Y4" s="50"/>
       <c r="Z4" s="18">
         <f t="shared" ref="Z4:Z22" si="5">$Y$3*(EXP(($Q$3)/($R$3*9.81))*(U4+V4)-(U4+V4))</f>
         <v>321.11590408121936</v>
@@ -41957,8 +41955,8 @@
       <c r="P5" s="7">
         <v>1880</v>
       </c>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="28"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="49"/>
       <c r="S5" s="7" t="s">
         <v>145</v>
       </c>
@@ -41980,7 +41978,7 @@
         <f t="shared" si="4"/>
         <v>422.520926422657</v>
       </c>
-      <c r="Y5" s="29"/>
+      <c r="Y5" s="50"/>
       <c r="Z5" s="18">
         <f t="shared" si="5"/>
         <v>481.67385612182892</v>
@@ -42042,8 +42040,8 @@
       <c r="P6" s="7">
         <v>2000</v>
       </c>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="28"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="49"/>
       <c r="U6" s="16">
         <v>400</v>
       </c>
@@ -42059,7 +42057,7 @@
         <f t="shared" si="4"/>
         <v>563.36123523020945</v>
       </c>
-      <c r="Y6" s="29"/>
+      <c r="Y6" s="50"/>
       <c r="Z6" s="18">
         <f t="shared" si="5"/>
         <v>642.23180816243871</v>
@@ -42124,8 +42122,8 @@
       <c r="P7" s="7">
         <v>1930</v>
       </c>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="28"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="49"/>
       <c r="S7" t="s">
         <v>147</v>
       </c>
@@ -42144,7 +42142,7 @@
         <f t="shared" si="4"/>
         <v>704.20154403776178</v>
       </c>
-      <c r="Y7" s="29"/>
+      <c r="Y7" s="50"/>
       <c r="Z7" s="18">
         <f t="shared" si="5"/>
         <v>802.78976020304833</v>
@@ -42209,8 +42207,8 @@
       <c r="P8" s="4">
         <v>3732</v>
       </c>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="28"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="49"/>
       <c r="S8" s="7" t="s">
         <v>144</v>
       </c>
@@ -42232,7 +42230,7 @@
         <f t="shared" si="4"/>
         <v>845.041852845314</v>
       </c>
-      <c r="Y8" s="29"/>
+      <c r="Y8" s="50"/>
       <c r="Z8" s="18">
         <f t="shared" si="5"/>
         <v>963.34771224365784</v>
@@ -42297,8 +42295,8 @@
       <c r="P9" s="4">
         <v>1880</v>
       </c>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="28"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="49"/>
       <c r="S9" s="7" t="s">
         <v>145</v>
       </c>
@@ -42320,7 +42318,7 @@
         <f t="shared" si="4"/>
         <v>985.88216165286644</v>
       </c>
-      <c r="Y9" s="29"/>
+      <c r="Y9" s="50"/>
       <c r="Z9" s="18">
         <f t="shared" si="5"/>
         <v>1123.9056642842677</v>
@@ -42385,8 +42383,8 @@
       <c r="P10" s="4">
         <v>1880</v>
       </c>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="28"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="49"/>
       <c r="U10" s="16">
         <v>800</v>
       </c>
@@ -42402,7 +42400,7 @@
         <f t="shared" si="4"/>
         <v>1126.7224704604189</v>
       </c>
-      <c r="Y10" s="29"/>
+      <c r="Y10" s="50"/>
       <c r="Z10" s="18">
         <f t="shared" si="5"/>
         <v>1284.4636163248774</v>
@@ -42467,8 +42465,8 @@
       <c r="P11" s="7">
         <v>1930</v>
       </c>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="28"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="49"/>
       <c r="U11" s="16">
         <v>900</v>
       </c>
@@ -42484,7 +42482,7 @@
         <f t="shared" si="4"/>
         <v>1267.5627792679711</v>
       </c>
-      <c r="Y11" s="29"/>
+      <c r="Y11" s="50"/>
       <c r="Z11" s="18">
         <f t="shared" si="5"/>
         <v>1445.0215683654869</v>
@@ -42526,7 +42524,7 @@
         <f t="shared" si="4"/>
         <v>1408.4030880755236</v>
       </c>
-      <c r="Y12" s="29"/>
+      <c r="Y12" s="50"/>
       <c r="Z12" s="18">
         <f t="shared" si="5"/>
         <v>1605.5795204060967</v>
@@ -42558,7 +42556,7 @@
         <f t="shared" si="4"/>
         <v>1549.2433968830755</v>
       </c>
-      <c r="Y13" s="29"/>
+      <c r="Y13" s="50"/>
       <c r="Z13" s="18">
         <f t="shared" si="5"/>
         <v>1766.1374724467059</v>
@@ -42590,7 +42588,7 @@
         <f t="shared" si="4"/>
         <v>1690.083705690628</v>
       </c>
-      <c r="Y14" s="29"/>
+      <c r="Y14" s="50"/>
       <c r="Z14" s="18">
         <f t="shared" si="5"/>
         <v>1926.6954244873157</v>
@@ -42622,7 +42620,7 @@
         <f t="shared" si="4"/>
         <v>1830.9240144981804</v>
       </c>
-      <c r="Y15" s="29"/>
+      <c r="Y15" s="50"/>
       <c r="Z15" s="18">
         <f t="shared" si="5"/>
         <v>2087.2533765279254</v>
@@ -42654,7 +42652,7 @@
         <f t="shared" si="4"/>
         <v>1971.7643233057329</v>
       </c>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="50"/>
       <c r="Z16" s="18">
         <f t="shared" si="5"/>
         <v>2247.8113285685354</v>
@@ -42686,7 +42684,7 @@
         <f t="shared" si="4"/>
         <v>2112.6046321132849</v>
       </c>
-      <c r="Y17" s="29"/>
+      <c r="Y17" s="50"/>
       <c r="Z17" s="18">
         <f t="shared" si="5"/>
         <v>2408.3692806091444</v>
@@ -42718,7 +42716,7 @@
         <f t="shared" si="4"/>
         <v>2253.4449409208378</v>
       </c>
-      <c r="Y18" s="29"/>
+      <c r="Y18" s="50"/>
       <c r="Z18" s="18">
         <f t="shared" si="5"/>
         <v>2568.9272326497548</v>
@@ -42747,7 +42745,7 @@
         <f t="shared" si="4"/>
         <v>2394.2852497283898</v>
       </c>
-      <c r="Y19" s="29"/>
+      <c r="Y19" s="50"/>
       <c r="Z19" s="18">
         <f t="shared" si="5"/>
         <v>2729.4851846903639</v>
@@ -42773,7 +42771,7 @@
         <f t="shared" si="4"/>
         <v>2535.1255585359422</v>
       </c>
-      <c r="Y20" s="29"/>
+      <c r="Y20" s="50"/>
       <c r="Z20" s="18">
         <f t="shared" si="5"/>
         <v>2890.0431367309739</v>
@@ -42799,7 +42797,7 @@
         <f t="shared" si="4"/>
         <v>2675.9658673434942</v>
       </c>
-      <c r="Y21" s="29"/>
+      <c r="Y21" s="50"/>
       <c r="Z21" s="18">
         <f t="shared" si="5"/>
         <v>3050.6010887715834</v>
@@ -42825,7 +42823,7 @@
         <f t="shared" si="4"/>
         <v>2816.8061761510471</v>
       </c>
-      <c r="Y22" s="29"/>
+      <c r="Y22" s="50"/>
       <c r="Z22" s="18">
         <f t="shared" si="5"/>
         <v>3211.1590408121933</v>
@@ -42993,10 +42991,10 @@
       <c r="K2" s="7">
         <v>2263</v>
       </c>
-      <c r="L2" s="25">
+      <c r="L2" s="46">
         <v>311</v>
       </c>
-      <c r="M2" s="30">
+      <c r="M2" s="51">
         <f>AVERAGE(K2:K8)</f>
         <v>2263.1428571428573</v>
       </c>
@@ -43018,7 +43016,7 @@
         <f>EXP(($M$2)/($L$2*9.81))*(Q2+R2)-(Q2+R2)</f>
         <v>6653.3827388882946</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="50">
         <v>1.1100000000000001</v>
       </c>
       <c r="V2" s="20">
@@ -43071,8 +43069,8 @@
       <c r="K3" s="7">
         <v>2263</v>
       </c>
-      <c r="L3" s="26"/>
-      <c r="M3" s="30"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="51"/>
       <c r="N3" s="7" t="s">
         <v>144</v>
       </c>
@@ -43094,7 +43092,7 @@
         <f>EXP(($M$2)/($L$2*9.81))*(Q3+R3)-(Q3+R3)</f>
         <v>6986.051875832708</v>
       </c>
-      <c r="U3" s="29"/>
+      <c r="U3" s="50"/>
       <c r="V3" s="20">
         <f t="shared" ref="V3:V32" si="3">$U$2*(EXP(($M$2)/($L$2*9.81))*(Q3+R3)-(Q3+R3))</f>
         <v>7754.5175821743069</v>
@@ -43145,8 +43143,8 @@
       <c r="K4" s="7">
         <v>2250</v>
       </c>
-      <c r="L4" s="26"/>
-      <c r="M4" s="30"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="51"/>
       <c r="N4" s="7" t="s">
         <v>145</v>
       </c>
@@ -43168,7 +43166,7 @@
         <f t="shared" ref="T4:T32" si="5">EXP(($M$2)/($L$2*9.81))*(Q4+R4)-(Q4+R4)</f>
         <v>7318.7210127771241</v>
       </c>
-      <c r="U4" s="29"/>
+      <c r="U4" s="50"/>
       <c r="V4" s="20">
         <f t="shared" si="3"/>
         <v>8123.7803241826086</v>
@@ -43219,8 +43217,8 @@
       <c r="K5" s="7">
         <v>2267</v>
       </c>
-      <c r="L5" s="26"/>
-      <c r="M5" s="30"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="51"/>
       <c r="Q5" s="7">
         <v>2300</v>
       </c>
@@ -43236,7 +43234,7 @@
         <f t="shared" si="5"/>
         <v>7651.3901497215384</v>
       </c>
-      <c r="U5" s="29"/>
+      <c r="U5" s="50"/>
       <c r="V5" s="20">
         <f t="shared" si="3"/>
         <v>8493.0430661909086</v>
@@ -43287,8 +43285,8 @@
       <c r="K6" s="7">
         <v>2265</v>
       </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="30"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="51"/>
       <c r="N6" t="s">
         <v>147</v>
       </c>
@@ -43307,7 +43305,7 @@
         <f t="shared" si="5"/>
         <v>7984.0592866659526</v>
       </c>
-      <c r="U6" s="29"/>
+      <c r="U6" s="50"/>
       <c r="V6" s="20">
         <f t="shared" si="3"/>
         <v>8862.3058081992076</v>
@@ -43358,8 +43356,8 @@
       <c r="K7" s="7">
         <v>2273</v>
       </c>
-      <c r="L7" s="26"/>
-      <c r="M7" s="30"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="51"/>
       <c r="N7" s="7" t="s">
         <v>144</v>
       </c>
@@ -43381,7 +43379,7 @@
         <f t="shared" si="5"/>
         <v>8316.7284236103678</v>
       </c>
-      <c r="U7" s="29"/>
+      <c r="U7" s="50"/>
       <c r="V7" s="20">
         <f t="shared" si="3"/>
         <v>9231.5685502075085</v>
@@ -43432,8 +43430,8 @@
       <c r="K8" s="7">
         <v>2261</v>
       </c>
-      <c r="L8" s="26"/>
-      <c r="M8" s="30"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="51"/>
       <c r="N8" s="7" t="s">
         <v>145</v>
       </c>
@@ -43455,7 +43453,7 @@
         <f t="shared" si="5"/>
         <v>8649.3975605547803</v>
       </c>
-      <c r="U8" s="29"/>
+      <c r="U8" s="50"/>
       <c r="V8" s="20">
         <f t="shared" si="3"/>
         <v>9600.8312922158075</v>
@@ -43487,7 +43485,7 @@
         <f t="shared" si="5"/>
         <v>8982.0666974991982</v>
       </c>
-      <c r="U9" s="29"/>
+      <c r="U9" s="50"/>
       <c r="V9" s="20">
         <f t="shared" si="3"/>
         <v>9970.0940342241101</v>
@@ -43519,7 +43517,7 @@
         <f t="shared" si="5"/>
         <v>9314.7358344436125</v>
       </c>
-      <c r="U10" s="29"/>
+      <c r="U10" s="50"/>
       <c r="V10" s="20">
         <f t="shared" si="3"/>
         <v>10339.356776232411</v>
@@ -43551,7 +43549,7 @@
         <f t="shared" si="5"/>
         <v>9647.4049713880268</v>
       </c>
-      <c r="U11" s="29"/>
+      <c r="U11" s="50"/>
       <c r="V11" s="20">
         <f t="shared" si="3"/>
         <v>10708.61951824071</v>
@@ -43583,7 +43581,7 @@
         <f t="shared" si="5"/>
         <v>9980.0741083324392</v>
       </c>
-      <c r="U12" s="29"/>
+      <c r="U12" s="50"/>
       <c r="V12" s="20">
         <f t="shared" si="3"/>
         <v>11077.882260249009</v>
@@ -43611,7 +43609,7 @@
         <f t="shared" si="5"/>
         <v>10312.743245276855</v>
       </c>
-      <c r="U13" s="29"/>
+      <c r="U13" s="50"/>
       <c r="V13" s="20">
         <f t="shared" si="3"/>
         <v>11447.14500225731</v>
@@ -43637,7 +43635,7 @@
         <f t="shared" si="5"/>
         <v>10645.412382221268</v>
       </c>
-      <c r="U14" s="29"/>
+      <c r="U14" s="50"/>
       <c r="V14" s="20">
         <f t="shared" si="3"/>
         <v>11816.407744265609</v>
@@ -43663,7 +43661,7 @@
         <f t="shared" si="5"/>
         <v>10978.081519165687</v>
       </c>
-      <c r="U15" s="29"/>
+      <c r="U15" s="50"/>
       <c r="V15" s="20">
         <f t="shared" si="3"/>
         <v>12185.670486273913</v>
@@ -43689,7 +43687,7 @@
         <f t="shared" si="5"/>
         <v>11310.7506561101</v>
       </c>
-      <c r="U16" s="29"/>
+      <c r="U16" s="50"/>
       <c r="V16" s="20">
         <f t="shared" si="3"/>
         <v>12554.933228282212</v>
@@ -43715,7 +43713,7 @@
         <f t="shared" si="5"/>
         <v>11643.419793054514</v>
       </c>
-      <c r="U17" s="29"/>
+      <c r="U17" s="50"/>
       <c r="V17" s="20">
         <f t="shared" si="3"/>
         <v>12924.195970290511</v>
@@ -43741,7 +43739,7 @@
         <f t="shared" si="5"/>
         <v>11976.088929998929</v>
       </c>
-      <c r="U18" s="29"/>
+      <c r="U18" s="50"/>
       <c r="V18" s="20">
         <f t="shared" si="3"/>
         <v>13293.458712298812</v>
@@ -43767,7 +43765,7 @@
         <f t="shared" si="5"/>
         <v>12308.758066943343</v>
       </c>
-      <c r="U19" s="29"/>
+      <c r="U19" s="50"/>
       <c r="V19" s="20">
         <f t="shared" si="3"/>
         <v>13662.721454307111</v>
@@ -43793,7 +43791,7 @@
         <f t="shared" si="5"/>
         <v>12641.427203887761</v>
       </c>
-      <c r="U20" s="29"/>
+      <c r="U20" s="50"/>
       <c r="V20" s="20">
         <f t="shared" si="3"/>
         <v>14031.984196315416</v>
@@ -43819,7 +43817,7 @@
         <f t="shared" si="5"/>
         <v>12974.096340832173</v>
       </c>
-      <c r="U21" s="29"/>
+      <c r="U21" s="50"/>
       <c r="V21" s="20">
         <f t="shared" si="3"/>
         <v>14401.246938323713</v>
@@ -43845,7 +43843,7 @@
         <f t="shared" si="5"/>
         <v>13306.765477776589</v>
       </c>
-      <c r="U22" s="29"/>
+      <c r="U22" s="50"/>
       <c r="V22" s="20">
         <f t="shared" si="3"/>
         <v>14770.509680332016</v>
@@ -43871,7 +43869,7 @@
         <f t="shared" si="5"/>
         <v>13639.434614721002</v>
       </c>
-      <c r="U23" s="29"/>
+      <c r="U23" s="50"/>
       <c r="V23" s="20">
         <f t="shared" si="3"/>
         <v>15139.772422340313</v>
@@ -43897,7 +43895,7 @@
         <f t="shared" si="5"/>
         <v>13972.103751665416</v>
       </c>
-      <c r="U24" s="29"/>
+      <c r="U24" s="50"/>
       <c r="V24" s="20">
         <f t="shared" si="3"/>
         <v>15509.035164348614</v>
@@ -43923,7 +43921,7 @@
         <f t="shared" si="5"/>
         <v>14304.77288860983</v>
       </c>
-      <c r="U25" s="29"/>
+      <c r="U25" s="50"/>
       <c r="V25" s="20">
         <f t="shared" si="3"/>
         <v>15878.297906356913</v>
@@ -43949,7 +43947,7 @@
         <f t="shared" si="5"/>
         <v>14637.442025554248</v>
       </c>
-      <c r="U26" s="29"/>
+      <c r="U26" s="50"/>
       <c r="V26" s="20">
         <f t="shared" si="3"/>
         <v>16247.560648365217</v>
@@ -43975,7 +43973,7 @@
         <f t="shared" si="5"/>
         <v>14970.111162498662</v>
       </c>
-      <c r="U27" s="29"/>
+      <c r="U27" s="50"/>
       <c r="V27" s="20">
         <f t="shared" si="3"/>
         <v>16616.823390373516</v>
@@ -44001,7 +43999,7 @@
         <f t="shared" si="5"/>
         <v>15302.780299443077</v>
       </c>
-      <c r="U28" s="29"/>
+      <c r="U28" s="50"/>
       <c r="V28" s="20">
         <f t="shared" si="3"/>
         <v>16986.086132381817</v>
@@ -44027,7 +44025,7 @@
         <f t="shared" si="5"/>
         <v>15635.449436387491</v>
       </c>
-      <c r="U29" s="29"/>
+      <c r="U29" s="50"/>
       <c r="V29" s="20">
         <f t="shared" si="3"/>
         <v>17355.348874390118</v>
@@ -44053,7 +44051,7 @@
         <f t="shared" si="5"/>
         <v>15968.118573331905</v>
       </c>
-      <c r="U30" s="29"/>
+      <c r="U30" s="50"/>
       <c r="V30" s="20">
         <f t="shared" si="3"/>
         <v>17724.611616398415</v>
@@ -44079,7 +44077,7 @@
         <f t="shared" si="5"/>
         <v>16300.787710276318</v>
       </c>
-      <c r="U31" s="29"/>
+      <c r="U31" s="50"/>
       <c r="V31" s="20">
         <f t="shared" si="3"/>
         <v>18093.874358406716</v>
@@ -44105,7 +44103,7 @@
         <f t="shared" si="5"/>
         <v>16633.456847220736</v>
       </c>
-      <c r="U32" s="29"/>
+      <c r="U32" s="50"/>
       <c r="V32" s="20">
         <f t="shared" si="3"/>
         <v>18463.137100415017</v>
@@ -44273,11 +44271,11 @@
       <c r="L2" s="7">
         <v>4380</v>
       </c>
-      <c r="M2" s="29">
+      <c r="M2" s="50">
         <f>AVERAGE(K2:K13)</f>
         <v>416.04166666666669</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="50">
         <f>AVERAGE(L2:L13)</f>
         <v>2968.6666666666665</v>
       </c>
@@ -44299,7 +44297,7 @@
         <f>EXP(($N$2)/($M$2*9.81))*(S2+T2)-(S2+T2)</f>
         <v>17011.947288085343</v>
       </c>
-      <c r="W2" s="31">
+      <c r="W2" s="52">
         <v>0.95</v>
       </c>
       <c r="X2" s="20">
@@ -44370,8 +44368,8 @@
       <c r="L3" s="7">
         <v>2520</v>
       </c>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
       <c r="P3" s="7" t="s">
         <v>144</v>
       </c>
@@ -44393,7 +44391,7 @@
         <f t="shared" ref="V3:V18" si="4">EXP(($N$2)/($M$2*9.81))*(S3+T3)-(S3+T3)</f>
         <v>18713.142016893871</v>
       </c>
-      <c r="W3" s="31"/>
+      <c r="W3" s="52"/>
       <c r="X3" s="20">
         <f t="shared" ref="X3:X18" si="5">V3*$W$2</f>
         <v>17777.484916049176</v>
@@ -44459,8 +44457,8 @@
         <v>450</v>
       </c>
       <c r="L4" s="7"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
       <c r="P4" s="7" t="s">
         <v>145</v>
       </c>
@@ -44482,7 +44480,7 @@
         <f t="shared" si="4"/>
         <v>20414.336745702414</v>
       </c>
-      <c r="W4" s="31"/>
+      <c r="W4" s="52"/>
       <c r="X4" s="20">
         <f t="shared" si="5"/>
         <v>19393.619908417291</v>
@@ -44538,8 +44536,8 @@
       <c r="L5" s="7">
         <v>1900</v>
       </c>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
       <c r="S5" s="7">
         <v>6500</v>
       </c>
@@ -44555,7 +44553,7 @@
         <f t="shared" si="4"/>
         <v>22115.531474510943</v>
       </c>
-      <c r="W5" s="31"/>
+      <c r="W5" s="52"/>
       <c r="X5" s="20">
         <f t="shared" si="5"/>
         <v>21009.754900785396</v>
@@ -44625,8 +44623,8 @@
       <c r="L6" s="7">
         <v>4380</v>
       </c>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="50"/>
       <c r="P6" t="s">
         <v>147</v>
       </c>
@@ -44645,7 +44643,7 @@
         <f t="shared" si="4"/>
         <v>23816.726203319482</v>
       </c>
-      <c r="W6" s="31"/>
+      <c r="W6" s="52"/>
       <c r="X6" s="20">
         <f t="shared" si="5"/>
         <v>22625.889893153508</v>
@@ -44715,8 +44713,8 @@
       <c r="L7" s="7">
         <v>4380</v>
       </c>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
       <c r="P7" s="7" t="s">
         <v>144</v>
       </c>
@@ -44738,7 +44736,7 @@
         <f t="shared" si="4"/>
         <v>25517.920932128014</v>
       </c>
-      <c r="W7" s="31"/>
+      <c r="W7" s="52"/>
       <c r="X7" s="20">
         <f t="shared" si="5"/>
         <v>24242.024885521612</v>
@@ -44806,8 +44804,8 @@
       <c r="L8" s="7">
         <v>2117</v>
       </c>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
       <c r="P8" s="7" t="s">
         <v>145</v>
       </c>
@@ -44829,7 +44827,7 @@
         <f t="shared" si="4"/>
         <v>27219.115660936543</v>
       </c>
-      <c r="W8" s="31"/>
+      <c r="W8" s="52"/>
       <c r="X8" s="20">
         <f t="shared" si="5"/>
         <v>25858.159877889713</v>
@@ -44899,8 +44897,8 @@
       <c r="L9" s="7">
         <v>2100</v>
       </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
       <c r="S9" s="7">
         <v>8500</v>
       </c>
@@ -44916,7 +44914,7 @@
         <f t="shared" si="4"/>
         <v>28920.310389745082</v>
       </c>
-      <c r="W9" s="31"/>
+      <c r="W9" s="52"/>
       <c r="X9" s="20">
         <f t="shared" si="5"/>
         <v>27474.294870257825</v>
@@ -44986,8 +44984,8 @@
       <c r="L10" s="7">
         <v>2100</v>
       </c>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
       <c r="S10" s="7">
         <v>9000</v>
       </c>
@@ -45003,7 +45001,7 @@
         <f t="shared" si="4"/>
         <v>30621.505118553614</v>
       </c>
-      <c r="W10" s="31"/>
+      <c r="W10" s="52"/>
       <c r="X10" s="20">
         <f t="shared" si="5"/>
         <v>29090.429862625933</v>
@@ -45069,8 +45067,8 @@
         <v>466</v>
       </c>
       <c r="L11" s="7"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="50"/>
       <c r="S11" s="7">
         <v>9500</v>
       </c>
@@ -45086,7 +45084,7 @@
         <f t="shared" si="4"/>
         <v>32322.699847362153</v>
       </c>
-      <c r="W11" s="31"/>
+      <c r="W11" s="52"/>
       <c r="X11" s="20">
         <f t="shared" si="5"/>
         <v>30706.564854994045</v>
@@ -45134,8 +45132,8 @@
         <v>465.5</v>
       </c>
       <c r="L12" s="7"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
       <c r="S12" s="7">
         <v>10000</v>
       </c>
@@ -45151,7 +45149,7 @@
         <f t="shared" si="4"/>
         <v>34023.894576170685</v>
       </c>
-      <c r="W12" s="31"/>
+      <c r="W12" s="52"/>
       <c r="X12" s="20">
         <f t="shared" si="5"/>
         <v>32322.69984736215</v>
@@ -45203,8 +45201,8 @@
       <c r="L13" s="7">
         <v>2841</v>
       </c>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
       <c r="S13" s="7">
         <v>10500</v>
       </c>
@@ -45220,7 +45218,7 @@
         <f t="shared" si="4"/>
         <v>35725.089304979221</v>
       </c>
-      <c r="W13" s="31"/>
+      <c r="W13" s="52"/>
       <c r="X13" s="20">
         <f t="shared" si="5"/>
         <v>33938.834839730262</v>
@@ -45261,7 +45259,7 @@
         <f t="shared" si="4"/>
         <v>37426.284033787742</v>
       </c>
-      <c r="W14" s="31"/>
+      <c r="W14" s="52"/>
       <c r="X14" s="20">
         <f t="shared" si="5"/>
         <v>35554.969832098352</v>
@@ -45287,7 +45285,7 @@
         <f t="shared" si="4"/>
         <v>39127.478762596285</v>
       </c>
-      <c r="W15" s="31"/>
+      <c r="W15" s="52"/>
       <c r="X15" s="20">
         <f t="shared" si="5"/>
         <v>37171.104824466471</v>
@@ -45313,7 +45311,7 @@
         <f t="shared" si="4"/>
         <v>40828.673491404828</v>
       </c>
-      <c r="W16" s="31"/>
+      <c r="W16" s="52"/>
       <c r="X16" s="20">
         <f t="shared" si="5"/>
         <v>38787.239816834583</v>
@@ -45339,7 +45337,7 @@
         <f t="shared" si="4"/>
         <v>42529.868220213364</v>
       </c>
-      <c r="W17" s="31"/>
+      <c r="W17" s="52"/>
       <c r="X17" s="20">
         <f t="shared" si="5"/>
         <v>40403.374809202694</v>
@@ -45365,7 +45363,7 @@
         <f t="shared" si="4"/>
         <v>44231.062949021885</v>
       </c>
-      <c r="W18" s="31"/>
+      <c r="W18" s="52"/>
       <c r="X18" s="20">
         <f t="shared" si="5"/>
         <v>42019.509801570792</v>
